--- a/sources/heihachi_step5.xlsx
+++ b/sources/heihachi_step5.xlsx
@@ -779,6 +779,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>f46ce297-20aa-42e9-8fad-54b3f4704d3d</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>f46ce297-20aa-42e9-8fad-54b3f4704d3d</t>
@@ -826,6 +831,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2bed6e68-3dcb-46ce-8b44-5a8ab9825180</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>2bed6e68-3dcb-46ce-8b44-5a8ab9825180</t>
@@ -871,6 +881,11 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>94e89bd5-df08-4d1f-954d-ff55d170def7</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -5364,6 +5379,11 @@
           <t>mhhLLmhhmm</t>
         </is>
       </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>5e401bff-867a-4231-89fe-31140fb8cfa3</t>
+        </is>
+      </c>
       <c r="Q94" t="inlineStr">
         <is>
           <t>5e401bff-867a-4231-89fe-31140fb8cfa3</t>
@@ -5396,6 +5416,11 @@
           <t>mhhLLmhhmm</t>
         </is>
       </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>4843994c-4a83-4e19-a59d-b3e33a4b6216</t>
+        </is>
+      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>4843994c-4a83-4e19-a59d-b3e33a4b6216</t>
@@ -5428,6 +5453,11 @@
           <t>mhhLLmhmmm</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>b75ce8db-3ddd-40cc-b908-e15c334e3eff</t>
+        </is>
+      </c>
       <c r="Q96" t="inlineStr">
         <is>
           <t>b75ce8db-3ddd-40cc-b908-e15c334e3eff</t>
@@ -5458,6 +5488,11 @@
       <c r="K97" t="inlineStr">
         <is>
           <t>hhhhmmlhmm</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>59b8bd40-2cec-44af-a5be-02b8f9c50b3c</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
